--- a/content-pipeline/inputs/book02/b02_ch02_final.xlsx
+++ b/content-pipeline/inputs/book02/b02_ch02_final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://transre-my.sharepoint.com/personal/fau_transre_com/Documents/_OneDrive/_Operational_Tools/Github/GCSEChinese/Inputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://transre-my.sharepoint.com/personal/fau_transre_com/Documents/_OneDrive/_Operational_Tools/Github/GCSEChinese/Inputs/Primary/二上/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_89C8B83967ABC6201C537DCD3958D0A110FE7844" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5C8D1B9-9E6D-4E39-A5ED-A7EDB53F4C96}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_89C8B83967ABC6201C537DCD3958D0A110FE7844" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4520EEB-E000-41BC-8458-D636134D5EF0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57600" yWindow="-16350" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Meta" sheetId="1" r:id="rId1"/>
@@ -160,204 +160,202 @@
     <t>English</t>
   </si>
   <si>
+    <t>頌熙</t>
+  </si>
+  <si>
+    <t>Song Xi (Name)</t>
+  </si>
+  <si>
+    <t>提議</t>
+  </si>
+  <si>
+    <t>suggest / suggestion</t>
+  </si>
+  <si>
+    <t>喫掉</t>
+  </si>
+  <si>
+    <t>eaten</t>
+  </si>
+  <si>
+    <t>贏</t>
+  </si>
+  <si>
+    <t>win / victory</t>
+  </si>
+  <si>
+    <t>寥寥幾筆</t>
+  </si>
+  <si>
+    <t>in just a few strokes.  Describes something done with minimal effort or detail, often used in the context of painting, writing, or sketching, implying simplicity and conciseness.</t>
+  </si>
+  <si>
+    <t>大搖大擺</t>
+  </si>
+  <si>
+    <t>Literally "big swing big sway," this idiom describes someone walking with an exaggerated, confident, or arrogant gait, often implying a sense of pride or defiance.</t>
+  </si>
+  <si>
+    <t>毫不示弱</t>
+  </si>
+  <si>
+    <t>This idiom means to not yield or show any sign of inferiority in the face of competition or confrontation. It is often used to describe someone who stands their ground or responds assertively without backing down</t>
+  </si>
+  <si>
+    <t>血盆大口</t>
+  </si>
+  <si>
+    <t>A Chinese idiom describing a mouth that is very large and fierce-looking, often used to depict a terrifying or ferocious animal or person, implying greed or menace.</t>
+  </si>
+  <si>
+    <t>難逃</t>
+  </si>
+  <si>
+    <t>cannot escape</t>
+  </si>
+  <si>
+    <t>鱷魚</t>
+  </si>
+  <si>
+    <t>crocodile / alligator</t>
+  </si>
+  <si>
+    <t>鯨魚</t>
+  </si>
+  <si>
+    <t>whale</t>
+  </si>
+  <si>
+    <t>浮現</t>
+  </si>
+  <si>
+    <t>emerge / appear</t>
+  </si>
+  <si>
+    <t>唰唰</t>
+  </si>
+  <si>
+    <t>swish. Describing a swift, continuous sound, like leaves rustling or something moving quickly through the air</t>
+  </si>
+  <si>
+    <t>強壯</t>
+  </si>
+  <si>
+    <t>strong</t>
+  </si>
+  <si>
+    <t>狡辯</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sophistry; to quibble; to argue speciously</t>
+  </si>
+  <si>
+    <t>沮喪</t>
+  </si>
+  <si>
+    <t>depressed / dejected / discouraged</t>
+  </si>
+  <si>
+    <t>Book 02 · Chapter 02: 一次有趣的畫畫比賽</t>
+  </si>
+  <si>
+    <t>REVIEW: check Pinyin (fix multi-pronunciation errors) and ContextSentence (fix if wrong or missing).</t>
+  </si>
+  <si>
+    <t>Traditional</t>
+  </si>
+  <si>
+    <t>Pinyin (auto - review!)</t>
+  </si>
+  <si>
+    <t>ContextSentence (auto - review!)</t>
+  </si>
+  <si>
+    <t>sòng xī</t>
+  </si>
+  <si>
+    <t>tí yì</t>
+  </si>
+  <si>
+    <t>突然，頌熙提議說：『小勇，我們來一次有趣的畫畫比賽吧。</t>
+  </si>
+  <si>
+    <t>chī diào</t>
+  </si>
+  <si>
+    <t>yíng</t>
+  </si>
+  <si>
+    <t>liáo liáo jǐ bǐ</t>
+  </si>
+  <si>
+    <t>dà yáo dà bǎi</t>
+  </si>
+  <si>
+    <t>看那隻狐狸，好像正大搖大擺心地走過來，要喫掉小雞呢。</t>
+  </si>
+  <si>
+    <t>háo bù shì ruò</t>
+  </si>
+  <si>
+    <t>頌熙毫不示弱，畫了一隻張着血盆大口的老虎，這下我的狼也難逃了。</t>
+  </si>
+  <si>
+    <t>xuè pén dà kǒu</t>
+  </si>
+  <si>
+    <t>nán táo</t>
+  </si>
+  <si>
+    <t>è yú</t>
+  </si>
+  <si>
+    <t>鱷魚，大象，還是鯨魚？</t>
+  </si>
+  <si>
+    <t>jīng yú</t>
+  </si>
+  <si>
+    <t>fú xiàn</t>
+  </si>
+  <si>
+    <t>突然，我的腦海裏浮現了『武松打虎』的畫面，我『唰唰』幾筆畫出一個強壯的巨人。</t>
+  </si>
+  <si>
+    <t>shuā shuā</t>
+  </si>
+  <si>
+    <t>qiáng zhuàng</t>
+  </si>
+  <si>
+    <t>Sophistry; to quibble; to argue speciously</t>
+  </si>
+  <si>
+    <t>jiǎo biàn</t>
+  </si>
+  <si>
+    <t>jǔ sàng</t>
+  </si>
+  <si>
+    <t>雖然輸了比賽，可是我一點也不沮喪，因為這次比賽實在太有趣了。</t>
+  </si>
+  <si>
+    <t>星期天，頌熙來我家做客。</t>
+  </si>
+  <si>
+    <t>誰畫的動物能喫掉對方畫的動物，就算贏，怎麼樣？</t>
+  </si>
+  <si>
+    <t>我先在紙上畫了一隻小雞，頌熙看了我一眼，寥寥幾筆就畫好了一隻狐狸。</t>
+  </si>
+  <si>
+    <t>『哈哈，你就別狡辯了，乖乖認輸吧！</t>
+  </si>
+  <si>
     <t>二上：一次有趣的畫畫比賽（第八頁）
 星期天，頌熙來我家做客。我們倆一會兒看電視，一會兒玩遊戲機。突然，頌熙提議說：『小勇，我們來一次有趣的畫畫比賽吧。我們倆輪流畫一隻小動物，誰畫的動物能喫掉對方畫的動物，就算贏，怎麼樣？』『嘿，這個主意真不錯。看我的，我一定會打敗你。』
 我先在紙上畫了一隻小雞，頌熙看了我一眼，寥寥幾筆就畫好了一隻狐狸。看那隻狐狸，好像正大搖大擺心地走過來，要喫掉小雞呢。我又畫了一隻狼，哼哼，看你的狐狸往哪裏逃？頌熙毫不示弱，畫了一隻張着血盆大口的老虎，這下我的狼也難逃了。我着急了：誰能喫掉老虎呢？鱷魚，大象，還是鯨魚？突然，我的腦海裏浮現了『武松打虎』的畫面，我『唰唰』幾筆畫出一個強壯的巨人。頌熙見了，高興地大喊道：『我的老虎能把你的人喫掉，你輸了，你輸了！』我不服氣，連忙說：『你沒聽過「武松打虎」的故事嗎？你說是人厲害還是老虎厲害？再說，老虎再厲害不也被關在動物園裏嗎？』『哈哈，你就別狡辯了，乖乖認輸吧！還記得規則嗎？可是畫小動物哦！』頌熙得意地說道。
-我無話可說，只好乖乖認輸了。雖然輸了比賽，可是我一點也不沮喪，因為這次比賽實在太有趣了。
-「成功了！」我高興地喊道。「我也做好了。」我朝旁邊一看，志文正得意洋洋地拿着一隻「小豬」。看它一隻眼睛大一隻眼睛小，我不禁「撲哧」笑出了聲。
-一隻隻可愛的小動物相繼在同學們的手中誕生，有小猴子、大象、老虎。。。還真是一次「動物聚會」呀。捏彩泥真有趣！</t>
-  </si>
-  <si>
-    <t>頌熙</t>
-  </si>
-  <si>
-    <t>Song Xi (Name)</t>
-  </si>
-  <si>
-    <t>提議</t>
-  </si>
-  <si>
-    <t>suggest / suggestion</t>
-  </si>
-  <si>
-    <t>喫掉</t>
-  </si>
-  <si>
-    <t>eaten</t>
-  </si>
-  <si>
-    <t>贏</t>
-  </si>
-  <si>
-    <t>win / victory</t>
-  </si>
-  <si>
-    <t>寥寥幾筆</t>
-  </si>
-  <si>
-    <t>in just a few strokes.  Describes something done with minimal effort or detail, often used in the context of painting, writing, or sketching, implying simplicity and conciseness.</t>
-  </si>
-  <si>
-    <t>大搖大擺</t>
-  </si>
-  <si>
-    <t>Literally "big swing big sway," this idiom describes someone walking with an exaggerated, confident, or arrogant gait, often implying a sense of pride or defiance.</t>
-  </si>
-  <si>
-    <t>毫不示弱</t>
-  </si>
-  <si>
-    <t>This idiom means to not yield or show any sign of inferiority in the face of competition or confrontation. It is often used to describe someone who stands their ground or responds assertively without backing down</t>
-  </si>
-  <si>
-    <t>血盆大口</t>
-  </si>
-  <si>
-    <t>A Chinese idiom describing a mouth that is very large and fierce-looking, often used to depict a terrifying or ferocious animal or person, implying greed or menace.</t>
-  </si>
-  <si>
-    <t>難逃</t>
-  </si>
-  <si>
-    <t>cannot escape</t>
-  </si>
-  <si>
-    <t>鱷魚</t>
-  </si>
-  <si>
-    <t>crocodile / alligator</t>
-  </si>
-  <si>
-    <t>鯨魚</t>
-  </si>
-  <si>
-    <t>whale</t>
-  </si>
-  <si>
-    <t>浮現</t>
-  </si>
-  <si>
-    <t>emerge / appear</t>
-  </si>
-  <si>
-    <t>唰唰</t>
-  </si>
-  <si>
-    <t>swish. Describing a swift, continuous sound, like leaves rustling or something moving quickly through the air</t>
-  </si>
-  <si>
-    <t>強壯</t>
-  </si>
-  <si>
-    <t>strong</t>
-  </si>
-  <si>
-    <t>狡辯</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sophistry; to quibble; to argue speciously</t>
-  </si>
-  <si>
-    <t>沮喪</t>
-  </si>
-  <si>
-    <t>depressed / dejected / discouraged</t>
-  </si>
-  <si>
-    <t>Book 02 · Chapter 02: 一次有趣的畫畫比賽</t>
-  </si>
-  <si>
-    <t>REVIEW: check Pinyin (fix multi-pronunciation errors) and ContextSentence (fix if wrong or missing).</t>
-  </si>
-  <si>
-    <t>Traditional</t>
-  </si>
-  <si>
-    <t>Pinyin (auto - review!)</t>
-  </si>
-  <si>
-    <t>ContextSentence (auto - review!)</t>
-  </si>
-  <si>
-    <t>sòng xī</t>
-  </si>
-  <si>
-    <t>tí yì</t>
-  </si>
-  <si>
-    <t>突然，頌熙提議說：『小勇，我們來一次有趣的畫畫比賽吧。</t>
-  </si>
-  <si>
-    <t>chī diào</t>
-  </si>
-  <si>
-    <t>yíng</t>
-  </si>
-  <si>
-    <t>liáo liáo jǐ bǐ</t>
-  </si>
-  <si>
-    <t>dà yáo dà bǎi</t>
-  </si>
-  <si>
-    <t>看那隻狐狸，好像正大搖大擺心地走過來，要喫掉小雞呢。</t>
-  </si>
-  <si>
-    <t>háo bù shì ruò</t>
-  </si>
-  <si>
-    <t>頌熙毫不示弱，畫了一隻張着血盆大口的老虎，這下我的狼也難逃了。</t>
-  </si>
-  <si>
-    <t>xuè pén dà kǒu</t>
-  </si>
-  <si>
-    <t>nán táo</t>
-  </si>
-  <si>
-    <t>è yú</t>
-  </si>
-  <si>
-    <t>鱷魚，大象，還是鯨魚？</t>
-  </si>
-  <si>
-    <t>jīng yú</t>
-  </si>
-  <si>
-    <t>fú xiàn</t>
-  </si>
-  <si>
-    <t>突然，我的腦海裏浮現了『武松打虎』的畫面，我『唰唰』幾筆畫出一個強壯的巨人。</t>
-  </si>
-  <si>
-    <t>shuā shuā</t>
-  </si>
-  <si>
-    <t>qiáng zhuàng</t>
-  </si>
-  <si>
-    <t>Sophistry; to quibble; to argue speciously</t>
-  </si>
-  <si>
-    <t>jiǎo biàn</t>
-  </si>
-  <si>
-    <t>jǔ sàng</t>
-  </si>
-  <si>
-    <t>雖然輸了比賽，可是我一點也不沮喪，因為這次比賽實在太有趣了。</t>
-  </si>
-  <si>
-    <t>星期天，頌熙來我家做客。</t>
-  </si>
-  <si>
-    <t>誰畫的動物能喫掉對方畫的動物，就算贏，怎麼樣？</t>
-  </si>
-  <si>
-    <t>我先在紙上畫了一隻小雞，頌熙看了我一眼，寥寥幾筆就畫好了一隻狐狸。</t>
-  </si>
-  <si>
-    <t>『哈哈，你就別狡辯了，乖乖認輸吧！</t>
+我無話可說，只好乖乖認輸了。雖然輸了比賽，可是我一點也不沮喪，因為這次比賽實在太有趣了。</t>
   </si>
 </sst>
 </file>
@@ -749,13 +747,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -763,7 +761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -771,7 +769,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -779,7 +777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -787,49 +785,49 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" s="2"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B9" s="2"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B12" s="2"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B13" s="2"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B14" s="2"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B15" s="2"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B16" s="2"/>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B17" s="2"/>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B19" s="2"/>
     </row>
   </sheetData>
@@ -841,14 +839,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="80" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -859,246 +857,246 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
       <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
       <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
         <v>21</v>
       </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
         <v>23</v>
       </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
         <v>25</v>
       </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
         <v>27</v>
       </c>
-      <c r="C10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
         <v>29</v>
       </c>
-      <c r="C11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
         <v>31</v>
       </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
         <v>33</v>
       </c>
-      <c r="C13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
         <v>35</v>
       </c>
-      <c r="C14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" t="s">
         <v>37</v>
       </c>
-      <c r="C15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
       <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
         <v>39</v>
       </c>
-      <c r="C16" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" t="s">
         <v>41</v>
       </c>
-      <c r="C17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="3"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="3"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" s="3"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
     </row>
   </sheetData>
@@ -1110,7 +1108,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
@@ -1118,258 +1116,258 @@
     <col min="4" max="4" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="4" t="s">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
         <v>48</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
         <v>51</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>20</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
         <v>53</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
         <v>68</v>
       </c>
-      <c r="D18" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>69</v>
-      </c>
-      <c r="D19" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>
